--- a/data/trans_dic/P1403-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1403-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,09; 18,73</t>
+          <t>12,99; 18,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 22,53</t>
+          <t>16,43; 22,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,74; 18,22</t>
+          <t>12,91; 17,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,68; 24,67</t>
+          <t>18,48; 24,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,25; 18,89</t>
+          <t>13,65; 18,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,28; 27,45</t>
+          <t>21,28; 28,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,73; 22,76</t>
+          <t>16,44; 22,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,8; 27,46</t>
+          <t>22,45; 26,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,77; 17,75</t>
+          <t>13,98; 17,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,84; 24,34</t>
+          <t>19,85; 24,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,48; 19,68</t>
+          <t>15,36; 19,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,56; 25,35</t>
+          <t>21,2; 24,98</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,11; 13,98</t>
+          <t>10,16; 14,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,29; 17,12</t>
+          <t>12,56; 17,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,32; 17,68</t>
+          <t>13,51; 18,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 18,25</t>
+          <t>15,32; 19,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,99; 21,16</t>
+          <t>15,73; 20,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,41; 21,44</t>
+          <t>16,11; 21,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,71; 19,52</t>
+          <t>14,46; 19,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,62; 21,29</t>
+          <t>17,22; 21,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,52; 16,85</t>
+          <t>13,49; 16,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,13; 18,4</t>
+          <t>15,05; 18,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,41; 18,08</t>
+          <t>14,63; 17,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,37; 18,8</t>
+          <t>16,71; 19,9</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 15,38</t>
+          <t>10,41; 15,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,08; 17,71</t>
+          <t>12,32; 17,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,74; 17,08</t>
+          <t>11,67; 17,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 22,69</t>
+          <t>17,07; 22,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,65; 20,36</t>
+          <t>14,53; 20,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,59; 20,49</t>
+          <t>14,38; 20,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 21,26</t>
+          <t>15,04; 21,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,25; 66,27</t>
+          <t>14,73; 19,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,17; 16,94</t>
+          <t>13,37; 17,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,14; 18,23</t>
+          <t>14,3; 18,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,27; 18,42</t>
+          <t>14,19; 18,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,11; 56,61</t>
+          <t>16,76; 20,26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,45; 14,47</t>
+          <t>10,5; 14,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,27; 21,56</t>
+          <t>16,29; 21,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,27; 17,84</t>
+          <t>13,22; 17,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,38; 22,23</t>
+          <t>16,8; 21,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 18,61</t>
+          <t>13,94; 18,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,72; 26,17</t>
+          <t>20,8; 26,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 20,0</t>
+          <t>14,88; 19,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,95; 25,1</t>
+          <t>21,16; 25,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,88; 15,93</t>
+          <t>12,84; 15,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,3; 23,23</t>
+          <t>19,26; 23,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 18,07</t>
+          <t>14,73; 18,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,74; 22,83</t>
+          <t>19,77; 22,72</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,96; 14,33</t>
+          <t>11,93; 14,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,45; 18,06</t>
+          <t>15,5; 18,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,95; 16,36</t>
+          <t>13,84; 16,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,0; 19,94</t>
+          <t>17,94; 20,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,77; 18,24</t>
+          <t>15,79; 18,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,46; 22,29</t>
+          <t>19,56; 22,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,45; 19,08</t>
+          <t>16,45; 19,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,3; 40,41</t>
+          <t>19,86; 22,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,25; 15,91</t>
+          <t>14,04; 15,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,01; 19,81</t>
+          <t>17,99; 19,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,52; 17,32</t>
+          <t>15,61; 17,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 29,88</t>
+          <t>19,27; 20,9</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136593</t>
+          <t>146841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>170007</t>
+          <t>180848</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>306600</t>
+          <t>327688</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90821; 129989</t>
+          <t>90152; 129110</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>115681; 158461</t>
+          <t>115554; 159406</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85976; 122953</t>
+          <t>87117; 121412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118620; 156624</t>
+          <t>127545; 168015</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>91176; 130024</t>
+          <t>93954; 129727</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>148358; 191308</t>
+          <t>148321; 196294</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>112554; 153156</t>
+          <t>110630; 153039</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>154012; 185457</t>
+          <t>164523; 197411</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>190327; 245365</t>
+          <t>193275; 247237</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>277843; 340831</t>
+          <t>278067; 342575</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>208587; 265202</t>
+          <t>206996; 261707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>282484; 332088</t>
+          <t>301597; 355372</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165963</t>
+          <t>182309</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>184738</t>
+          <t>204022</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>350702</t>
+          <t>386331</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97246; 134453</t>
+          <t>97675; 138170</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>125129; 174276</t>
+          <t>127862; 175155</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136234; 180757</t>
+          <t>138139; 185711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73806; 217610</t>
+          <t>160545; 206170</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>154833; 204893</t>
+          <t>152290; 202883</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>168817; 220576</t>
+          <t>165759; 219195</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>153380; 203533</t>
+          <t>150757; 200384</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168640; 203695</t>
+          <t>184142; 224823</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>260916; 325235</t>
+          <t>260356; 325932</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>309605; 376667</t>
+          <t>308024; 376286</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>297665; 373446</t>
+          <t>302106; 370831</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>222849; 404012</t>
+          <t>353851; 421317</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136687</t>
+          <t>158230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>321640</t>
+          <t>136565</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>458327</t>
+          <t>294794</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>67338; 104372</t>
+          <t>70608; 105046</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91525; 134184</t>
+          <t>93345; 136041</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>89157; 129733</t>
+          <t>88647; 129804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116978; 159476</t>
+          <t>136544; 182830</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100157; 139224</t>
+          <t>99372; 137223</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>113216; 159016</t>
+          <t>111563; 157173</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>119298; 166923</t>
+          <t>118073; 165350</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>142115; 617605</t>
+          <t>119357; 154688</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>179391; 230752</t>
+          <t>182205; 233573</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>216816; 279626</t>
+          <t>219392; 278133</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>220436; 284571</t>
+          <t>219220; 281725</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>279732; 925513</t>
+          <t>269866; 326214</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182010</t>
+          <t>187890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>243593</t>
+          <t>259673</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>425603</t>
+          <t>447563</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98477; 136319</t>
+          <t>98935; 135643</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>154195; 204352</t>
+          <t>154426; 206711</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124393; 167286</t>
+          <t>123951; 166233</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>160886; 205770</t>
+          <t>166121; 211276</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>146026; 193267</t>
+          <t>144815; 190769</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>218003; 275292</t>
+          <t>218816; 274088</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>156015; 208771</t>
+          <t>155344; 207088</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>195820; 273792</t>
+          <t>236279; 284570</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>255062; 315618</t>
+          <t>254394; 315277</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>385993; 464565</t>
+          <t>385084; 462146</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>292571; 357947</t>
+          <t>291810; 362039</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>377911; 460379</t>
+          <t>416347; 478384</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>621253</t>
+          <t>675270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>919978</t>
+          <t>781108</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1541231</t>
+          <t>1456378</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>391893; 469366</t>
+          <t>390835; 467759</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>529427; 618780</t>
+          <t>531292; 625083</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473573; 555243</t>
+          <t>469734; 553028</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>483909; 689114</t>
+          <t>632575; 724668</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>533039; 616523</t>
+          <t>533685; 618416</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>691577; 792112</t>
+          <t>695173; 796731</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>582971; 676205</t>
+          <t>583146; 679166</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>742025; 1477015</t>
+          <t>740525; 822721</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>948521; 1059189</t>
+          <t>934256; 1053357</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1257558; 1382834</t>
+          <t>1256085; 1389061</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1077061; 1201718</t>
+          <t>1083303; 1215326</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1335900; 2124866</t>
+          <t>1398603; 1516704</t>
         </is>
       </c>
     </row>
